--- a/AAII_Financials/Quarterly/VNRFY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/VNRFY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="92">
   <si>
     <t>VNRFY</t>
   </si>
@@ -656,94 +656,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -786,20 +794,26 @@
       <c r="P8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3">
         <v>5766000</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U8" s="3">
         <v>71900</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="V8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -842,20 +856,26 @@
       <c r="P9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3">
         <v>1198700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>682000</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T9" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -898,20 +918,26 @@
       <c r="P10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3">
         <v>4567300</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -932,8 +958,10 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -988,8 +1016,14 @@
       <c r="T12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1044,8 +1078,14 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1088,20 +1128,26 @@
       <c r="P14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3">
         <v>25500</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U14" s="3">
         <v>1500</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="V14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1150,14 +1196,20 @@
       <c r="R15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
-      </c>
-      <c r="T15" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1175,8 +1227,10 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1219,20 +1273,26 @@
       <c r="P17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3">
         <v>5484300</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U17" s="3">
         <v>-424000</v>
       </c>
-      <c r="T17" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="V17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1275,20 +1335,26 @@
       <c r="P18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3">
         <v>281600</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U18" s="3">
         <v>495900</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="V18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1309,8 +1375,10 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1353,20 +1421,26 @@
       <c r="P20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R20" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U20" s="3">
         <v>-176100</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="V20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1421,8 +1495,14 @@
       <c r="T21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1465,20 +1545,26 @@
       <c r="P22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>49100</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="V22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1521,20 +1607,26 @@
       <c r="P23" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3">
         <v>281600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>135700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>270700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>137800</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1577,20 +1669,26 @@
       <c r="P24" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="3">
         <v>67700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>36900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>65400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>30000</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1645,8 +1743,14 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1689,20 +1793,26 @@
       <c r="P26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3">
         <v>214000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>98800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>205400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>107800</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1745,20 +1855,26 @@
       <c r="P27" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3">
         <v>205400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>96100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>200700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>106600</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1813,8 +1929,14 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1857,11 +1979,11 @@
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -1869,8 +1991,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1925,8 +2053,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1981,8 +2115,14 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2025,20 +2165,26 @@
       <c r="P32" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="R32" s="3" t="s">
         <v>4</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U32" s="3">
         <v>176100</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="V32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2081,20 +2227,26 @@
       <c r="P33" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3">
         <v>205400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>96100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>200700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>106600</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2149,8 +2301,14 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2193,81 +2351,93 @@
       <c r="P35" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3">
         <v>205400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>96100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>200700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>106600</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2288,8 +2458,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2310,176 +2482,196 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1747300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>1763400</v>
+      </c>
+      <c r="F41" s="3">
         <v>1606600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>1605500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>1948300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1793100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1809800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>1949700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2079100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>2093400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1722200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1649100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1936700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1927400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>2200500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>2654600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>3121800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>3200900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>2655600</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>15387000</v>
+      </c>
+      <c r="E42" s="3">
+        <v>15528900</v>
+      </c>
+      <c r="F42" s="3">
         <v>14709600</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>14699300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>13765400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>12668800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>11854700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>12771000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>11063800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>11140200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>11702800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>11206100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>11351200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>11296900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>191000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
       <c r="S42" s="3">
         <v>0</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1668900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1684300</v>
+      </c>
+      <c r="F43" s="3">
         <v>1468300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1467300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1342500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1235600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1139000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1227000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1165000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1173100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>1062100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>1017000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>982600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>977900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1985400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>2234000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>2021700</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
-      <c r="T43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2522,11 +2714,11 @@
       <c r="P44" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
-      <c r="R44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R44" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S44" s="3">
         <v>0</v>
@@ -2534,288 +2726,324 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>2967800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>2995100</v>
+      </c>
+      <c r="F45" s="3">
         <v>2905700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>2903700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>2450200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>2255000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>2236800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>2409700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1978400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1992000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>2019800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1934100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>2153200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>2142900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>3088700</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
-      <c r="R45" s="3">
-        <v>0</v>
-      </c>
       <c r="S45" s="3">
         <v>0</v>
       </c>
       <c r="T45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+      <c r="V45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>21771000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>21971800</v>
+      </c>
+      <c r="F46" s="3">
         <v>20690300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>20675700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>19506400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>17952500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>17040300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>18357400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>16286300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>16398800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>16507000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>15806400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>17738400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>17653600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>7465600</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
-      <c r="R46" s="3">
-        <v>0</v>
-      </c>
       <c r="S46" s="3">
+        <v>0</v>
+      </c>
+      <c r="T46" s="3">
+        <v>0</v>
+      </c>
+      <c r="U46" s="3">
         <v>3200900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>2655600</v>
       </c>
     </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3858800</v>
+      </c>
+      <c r="E47" s="3">
+        <v>3894400</v>
+      </c>
+      <c r="F47" s="3">
         <v>2866500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>2864500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>2791100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>2568800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>2381900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>2566000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>29125400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>29326500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>29652900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>28394400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>27081100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>26951700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>28636900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>34684300</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>37872400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>36629400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>39527600</v>
       </c>
     </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1009600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1018900</v>
+      </c>
+      <c r="F48" s="3">
         <v>1029400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1028700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>999500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>919900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>871300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>938600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>859800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>865700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>897500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>859400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>887500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>883300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>339600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>3268000</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U48" s="3">
         <v>2913400</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="V48" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2176000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>2196100</v>
+      </c>
+      <c r="F49" s="3">
         <v>2228000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>2226500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>2210800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>2034600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>2005100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>2160100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2109100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>2123600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2168400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2076300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2259000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>2248200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>2228000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1884900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>2064100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>1873800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>2052600</v>
       </c>
     </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2870,8 +3098,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2926,64 +3160,76 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3760000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3794700</v>
+      </c>
+      <c r="F52" s="3">
         <v>3778400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>3775700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>3694200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>3400000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>3243800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>3494500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3250600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>3273100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>3309000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>3168600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>3091400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>3076700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>11115800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>336600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>263300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>11365300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>11233100</v>
       </c>
     </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3038,64 +3284,76 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>64782500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>65380000</v>
+      </c>
+      <c r="F54" s="3">
         <v>63773200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>63728300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>61321400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>56436600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>53051100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>57151500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>52906900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>53272200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>53889500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>51602200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>52545200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>52294000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>52660100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>56388900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>56745500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>55982800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>55469000</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3116,8 +3374,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3138,103 +3398,111 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>11471700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>11577600</v>
+      </c>
+      <c r="F57" s="3">
         <v>10988700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>10981000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>10359000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>9533900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>8588200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>9252000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>8440600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>8498900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>8279100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>7927700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>18600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>18500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>5703500</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
       <c r="T57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>205800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>205700</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>173200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>186600</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3">
         <v>164400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>157400</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -3250,232 +3518,262 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>376300</v>
+      </c>
+      <c r="E59" s="3">
+        <v>379800</v>
+      </c>
+      <c r="F59" s="3">
         <v>1780900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>1779600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>317100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>291800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>1292900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>1392900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>202400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>203800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>1056700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>1011900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>169300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>168500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>2592200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>37891700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>44670900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>45162000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>43786800</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>11848000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>11957300</v>
+      </c>
+      <c r="F60" s="3">
         <v>12975400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>12966300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>10676100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>9825700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>10054300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>10831400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>8643000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>8702700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>9500200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>9097000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>187900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>187000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>9049300</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
-      <c r="R60" s="3">
-        <v>0</v>
-      </c>
       <c r="S60" s="3">
+        <v>0</v>
+      </c>
+      <c r="T60" s="3">
+        <v>0</v>
+      </c>
+      <c r="U60" s="3">
         <v>45162000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>43786800</v>
       </c>
     </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2887300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2913900</v>
+      </c>
+      <c r="F61" s="3">
         <v>2629500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>2627700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1942200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1787500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>2221300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>2393000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1703600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1715400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>2482300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>2377000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>2910000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>2896100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>3065500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1958600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1589700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>2144400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>1572300</v>
       </c>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>40488700</v>
+      </c>
+      <c r="E62" s="3">
+        <v>40862200</v>
+      </c>
+      <c r="F62" s="3">
         <v>38741300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>38714100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>39869400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>36693500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>33204500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>35770900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>35208000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>35451100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>34456600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>32994200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>42220000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>42018200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>35430800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>819300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>286200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>2646700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>4444400</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3530,8 +3828,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3586,8 +3890,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3642,64 +3952,76 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>56094200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>56611600</v>
+      </c>
+      <c r="F66" s="3">
         <v>55165300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>55126400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>53387200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>49134500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>46260600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>49836200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>46314600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>46634400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>47224600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>45220200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>46036700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>45816600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>47921200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>50468600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>50644500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>50071500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>49803400</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3720,8 +4042,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3776,8 +4100,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3832,8 +4162,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3888,8 +4224,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3944,64 +4286,76 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5563900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>5615200</v>
+      </c>
+      <c r="F72" s="3">
         <v>5398700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>5394900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>4828700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>4444100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>4119200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>4437600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>3910300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>3937300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>3857800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>3694000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>3737800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>3719900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>3306800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>5452500</v>
       </c>
-      <c r="R72" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U72" s="3">
         <v>5663700</v>
       </c>
-      <c r="T72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="V72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4056,8 +4410,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4112,8 +4472,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4168,64 +4534,76 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8498100</v>
+      </c>
+      <c r="E76" s="3">
+        <v>8576500</v>
+      </c>
+      <c r="F76" s="3">
         <v>8419500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>8413500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>7765400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>7146800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>6638200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>7151200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>6446400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>6491000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>6513000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>6236500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>6244000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>6214100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>4514100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>5920300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>6101000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>5911400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>5666600</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4280,69 +4658,81 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>44286</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4385,20 +4775,26 @@
       <c r="P81" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3">
         <v>205400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>96100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>200700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>106600</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4419,41 +4815,43 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-185600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>-170800</v>
+      </c>
+      <c r="F83" s="3">
         <v>408500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>440100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>-301600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>-303700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>391100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>374500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>-303000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>-301500</v>
       </c>
-      <c r="L83" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N83" s="3" t="s">
         <v>4</v>
       </c>
@@ -4463,11 +4861,11 @@
       <c r="P83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S83" s="3">
         <v>0</v>
@@ -4475,8 +4873,14 @@
       <c r="T83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4531,8 +4935,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4587,8 +4997,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4643,8 +5059,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4699,8 +5121,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4755,64 +5183,76 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>294200</v>
+      </c>
+      <c r="E89" s="3">
+        <v>296900</v>
+      </c>
+      <c r="F89" s="3">
         <v>174500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>174400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>320000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>294500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>110500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>119100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>71000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>71500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-6400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-6100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-69700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-69400</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S89" s="3">
         <v>572900</v>
       </c>
-      <c r="R89" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T89" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4833,55 +5273,57 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-77500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-78200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-69300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-69200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-52800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-48600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-72700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-78300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-44600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-44900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-99200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-95000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-46600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-46400</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="R91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -4889,8 +5331,14 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4945,8 +5393,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5001,64 +5455,76 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-89300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-90100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-275100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-274900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-278700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-256500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-144200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-155300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>287300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>289300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>221000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>211600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>49100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>48900</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S94" s="3">
         <v>-449100</v>
       </c>
-      <c r="R94" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T94" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5079,64 +5545,72 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>137900</v>
+      </c>
+      <c r="E96" s="3">
+        <v>139200</v>
+      </c>
+      <c r="F96" s="3">
         <v>200</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>130400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>120000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>100</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>107000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>107700</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P96" s="3">
         <v>102200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>101700</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S96" s="3">
         <v>-103700</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
-      <c r="S96" s="3">
-        <v>0</v>
-      </c>
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5191,8 +5665,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5247,8 +5727,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5303,97 +5789,109 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-111100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-112100</v>
+      </c>
+      <c r="F100" s="3">
         <v>-71400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-71300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-82500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-75900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-67000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-72100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-150200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-151200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-335600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-321400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-269300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-268100</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S100" s="3">
         <v>646000</v>
       </c>
-      <c r="R100" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S100" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-11100</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>-10200</v>
       </c>
       <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-7300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-7400</v>
       </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
       <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>-8400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-8400</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="N101" s="3" t="s">
         <v>4</v>
       </c>
@@ -5403,72 +5901,84 @@
       <c r="P101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S101" s="3">
         <v>-1200</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S101" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>92800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>93700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-172900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-172700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-52200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-48100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-100600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-108400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>200800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>202200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-121100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-115900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-298400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-297000</v>
       </c>
-      <c r="P102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>768600</v>
       </c>
-      <c r="R102" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>4</v>
       </c>
     </row>
